--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129479392</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57721</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gröndal Skogen, Solberga, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484477</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6398403</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johanna Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129479392</v>
       </c>
       <c r="B3" t="n">
-        <v>57721</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129479392</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>129479392</v>
       </c>
       <c r="B3" t="n">
-        <v>57729</v>
+        <v>57730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -893,6 +893,329 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130020001</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gröndal, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>484471</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6398282</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130019412</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92255</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gröndal, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>484475</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6398436</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130019407</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98797</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gröndal, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>484478</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6398407</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>130019412</v>
       </c>
       <c r="B5" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>130019407</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>130020001</v>
       </c>
       <c r="B4" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130019412</v>
       </c>
       <c r="B5" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>130019407</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -1003,7 +1003,7 @@
         <v>130019412</v>
       </c>
       <c r="B5" t="n">
-        <v>92289</v>
+        <v>92291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>130019407</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
         <v>130020001</v>
       </c>
       <c r="B4" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>130019412</v>
       </c>
       <c r="B5" t="n">
-        <v>92291</v>
+        <v>92378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>130019407</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,66 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118803156</v>
+        <v>130019408</v>
       </c>
       <c r="B2" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gröndal Skogen, Solberga, Sm</t>
+          <t>Gröndal, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484477</v>
+        <v>484453</v>
       </c>
       <c r="R2" t="n">
-        <v>6398403</v>
+        <v>6398393</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,25 +761,45 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johanna Andersson</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Andersson</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129479392</v>
+        <v>130019412</v>
       </c>
       <c r="B3" t="n">
-        <v>57730</v>
+        <v>92564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,38 +807,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gröndal Skogen, Solberga, Sm</t>
+          <t>Gröndal, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484477</v>
+        <v>484475</v>
       </c>
       <c r="R3" t="n">
-        <v>6398403</v>
+        <v>6398436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,28 +878,49 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johanna Andersson</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Andersson</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130020001</v>
+        <v>129479392</v>
       </c>
       <c r="B4" t="n">
-        <v>58198</v>
+        <v>57947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,42 +928,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>102977</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gröndal, Sm</t>
+          <t>Gröndal Skogen, Solberga, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484471</v>
+        <v>484477</v>
       </c>
       <c r="R4" t="n">
-        <v>6398282</v>
+        <v>6398403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,12 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,22 +1006,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Johanna Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Johanna Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130019412</v>
+        <v>130020001</v>
       </c>
       <c r="B5" t="n">
-        <v>92378</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,26 +1029,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1038,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484475</v>
+        <v>484471</v>
       </c>
       <c r="R5" t="n">
-        <v>6398436</v>
+        <v>6398282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,29 +1105,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1121,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130019407</v>
+        <v>118803156</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,17 +1151,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gröndal, Sm</t>
+          <t>Gröndal Skogen, Solberga, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484478</v>
+        <v>484477</v>
       </c>
       <c r="R6" t="n">
-        <v>6398407</v>
+        <v>6398403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,12 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,21 +1218,119 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Johanna Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johanna Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130019407</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gröndal, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>484478</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6398407</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nässjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Solberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45048-2025 artfynd.xlsx
+++ b/artfynd/A 45048-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130019408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130019412</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129479392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130020001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118803156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,8 +1361,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130019407</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>